--- a/lien_dreame.xlsx
+++ b/lien_dreame.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/Recherche Sharepoint/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{1CDDBA96-09C2-43AA-AE1D-ADFCE59AF47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43914C1A-0BD4-41CE-94D5-84EA0C388EA6}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{1CDDBA96-09C2-43AA-AE1D-ADFCE59AF47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A4BD40B-66B2-4166-B152-076A58356E1A}"/>
   <bookViews>
     <workbookView xWindow="43097" yWindow="-103" windowWidth="38606" windowHeight="21086" xr2:uid="{B13511EB-A0AF-4947-9D74-2425DEE1382B}"/>
   </bookViews>
@@ -6387,7 +6387,7 @@
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.3046875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="80.61328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="138.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
